--- a/docs/levelups.xlsx
+++ b/docs/levelups.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="220">
   <si>
     <t>viking shortsword</t>
   </si>
@@ -655,6 +655,27 @@
   </si>
   <si>
     <t>up to 6 items can be found in any container.</t>
+  </si>
+  <si>
+    <t>tier 2 rooms</t>
+  </si>
+  <si>
+    <t>tier  1 rooms</t>
+  </si>
+  <si>
+    <t>tier 5 rooms</t>
+  </si>
+  <si>
+    <t>tier 3 rooms</t>
+  </si>
+  <si>
+    <t>tier 4 rooms</t>
+  </si>
+  <si>
+    <t>tier 4, 5 rooms</t>
+  </si>
+  <si>
+    <t>location</t>
   </si>
 </sst>
 </file>
@@ -1085,6 +1106,9 @@
       <c r="E3">
         <v>4</v>
       </c>
+      <c r="F3" t="s">
+        <v>205</v>
+      </c>
       <c r="G3">
         <v>68</v>
       </c>
@@ -1105,6 +1129,9 @@
       <c r="E4">
         <v>5</v>
       </c>
+      <c r="F4" t="s">
+        <v>213</v>
+      </c>
       <c r="G4">
         <v>69</v>
       </c>
@@ -1125,6 +1152,9 @@
       <c r="E5">
         <v>6</v>
       </c>
+      <c r="F5" t="s">
+        <v>213</v>
+      </c>
       <c r="G5">
         <v>70</v>
       </c>
@@ -1168,6 +1198,9 @@
       <c r="E7">
         <v>7</v>
       </c>
+      <c r="F7" t="s">
+        <v>205</v>
+      </c>
       <c r="G7">
         <v>87</v>
       </c>
@@ -1188,6 +1221,9 @@
       <c r="E8">
         <v>7</v>
       </c>
+      <c r="F8" t="s">
+        <v>214</v>
+      </c>
       <c r="G8">
         <v>88</v>
       </c>
@@ -1208,6 +1244,9 @@
       <c r="E9">
         <v>8</v>
       </c>
+      <c r="F9" t="s">
+        <v>213</v>
+      </c>
       <c r="G9">
         <v>89</v>
       </c>
@@ -1228,6 +1267,9 @@
       <c r="E10">
         <v>8</v>
       </c>
+      <c r="F10" t="s">
+        <v>213</v>
+      </c>
       <c r="G10">
         <v>90</v>
       </c>
@@ -1271,6 +1313,9 @@
       <c r="E12">
         <v>9</v>
       </c>
+      <c r="F12" t="s">
+        <v>213</v>
+      </c>
       <c r="G12">
         <v>98</v>
       </c>
@@ -1291,6 +1336,9 @@
       <c r="E13">
         <v>10</v>
       </c>
+      <c r="F13" t="s">
+        <v>216</v>
+      </c>
       <c r="G13">
         <v>99</v>
       </c>
@@ -1311,6 +1359,9 @@
       <c r="E14">
         <v>10</v>
       </c>
+      <c r="F14" t="s">
+        <v>218</v>
+      </c>
       <c r="G14">
         <v>100</v>
       </c>
@@ -1354,6 +1405,9 @@
       <c r="E16">
         <v>5</v>
       </c>
+      <c r="F16" t="s">
+        <v>213</v>
+      </c>
       <c r="G16">
         <v>79</v>
       </c>
@@ -1374,6 +1428,9 @@
       <c r="E17">
         <v>6</v>
       </c>
+      <c r="F17" t="s">
+        <v>216</v>
+      </c>
       <c r="G17">
         <v>80</v>
       </c>
@@ -1417,6 +1474,9 @@
       <c r="E19">
         <v>1</v>
       </c>
+      <c r="F19" t="s">
+        <v>205</v>
+      </c>
       <c r="G19">
         <v>53</v>
       </c>
@@ -1437,6 +1497,9 @@
       <c r="E20">
         <v>1</v>
       </c>
+      <c r="F20" t="s">
+        <v>213</v>
+      </c>
       <c r="G20">
         <v>54</v>
       </c>
@@ -1457,6 +1520,9 @@
       <c r="E21">
         <v>2</v>
       </c>
+      <c r="F21" t="s">
+        <v>213</v>
+      </c>
       <c r="G21">
         <v>55</v>
       </c>
@@ -1477,6 +1543,9 @@
       <c r="E22">
         <v>2</v>
       </c>
+      <c r="F22" t="s">
+        <v>216</v>
+      </c>
       <c r="G22">
         <v>56</v>
       </c>
@@ -1497,6 +1566,9 @@
       <c r="E23">
         <v>2</v>
       </c>
+      <c r="F23" t="s">
+        <v>216</v>
+      </c>
       <c r="G23">
         <v>57</v>
       </c>
@@ -1517,6 +1589,9 @@
       <c r="E24">
         <v>3</v>
       </c>
+      <c r="F24" t="s">
+        <v>217</v>
+      </c>
       <c r="G24">
         <v>58</v>
       </c>
@@ -1537,6 +1612,9 @@
       <c r="E25">
         <v>3</v>
       </c>
+      <c r="F25" t="s">
+        <v>217</v>
+      </c>
       <c r="G25">
         <v>59</v>
       </c>
@@ -1557,6 +1635,9 @@
       <c r="E26">
         <v>3</v>
       </c>
+      <c r="F26" t="s">
+        <v>215</v>
+      </c>
       <c r="G26">
         <v>60</v>
       </c>
@@ -1577,6 +1658,9 @@
       <c r="E27">
         <v>4</v>
       </c>
+      <c r="F27" t="s">
+        <v>205</v>
+      </c>
       <c r="G27">
         <v>72</v>
       </c>
@@ -1597,6 +1681,9 @@
       <c r="E28">
         <v>4</v>
       </c>
+      <c r="F28" t="s">
+        <v>213</v>
+      </c>
       <c r="G28">
         <v>73</v>
       </c>
@@ -1617,6 +1704,9 @@
       <c r="E29">
         <v>5</v>
       </c>
+      <c r="F29" t="s">
+        <v>216</v>
+      </c>
       <c r="G29">
         <v>74</v>
       </c>
@@ -1636,6 +1726,9 @@
       </c>
       <c r="E30">
         <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>218</v>
       </c>
       <c r="G30">
         <v>75</v>
@@ -1691,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.06640625" customWidth="1"/>
@@ -1699,9 +1792,10 @@
     <col min="3" max="3" width="22.9296875" customWidth="1"/>
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
     <col min="5" max="5" width="18.265625" customWidth="1"/>
+    <col min="6" max="6" width="19.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -1717,8 +1811,11 @@
       <c r="E1" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F1" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1734,8 +1831,11 @@
       <c r="E2">
         <v>510</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1751,8 +1851,11 @@
       <c r="E3">
         <v>525</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -1768,8 +1871,11 @@
       <c r="E4">
         <v>525</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -1785,8 +1891,11 @@
       <c r="E5">
         <v>550</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1802,8 +1911,11 @@
       <c r="E6">
         <v>575</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1819,8 +1931,11 @@
       <c r="E7">
         <v>600</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1836,8 +1951,11 @@
       <c r="E8">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -1853,8 +1971,11 @@
       <c r="E9">
         <v>475</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1870,8 +1991,11 @@
       <c r="E10">
         <v>500</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1887,8 +2011,11 @@
       <c r="E11">
         <v>400</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1904,8 +2031,11 @@
       <c r="E12">
         <v>375</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1921,8 +2051,11 @@
       <c r="E13">
         <v>200</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -1938,8 +2071,11 @@
       <c r="E14">
         <v>175</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -1955,8 +2091,11 @@
       <c r="E15">
         <v>150</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -1972,8 +2111,11 @@
       <c r="E16">
         <v>210</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -1989,8 +2131,11 @@
       <c r="E17">
         <v>225</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F17" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -2006,8 +2151,11 @@
       <c r="E18">
         <v>250</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F18" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -2023,8 +2171,11 @@
       <c r="E19">
         <v>275</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F19" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -2040,8 +2191,11 @@
       <c r="E20">
         <v>300</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -2057,8 +2211,11 @@
       <c r="E21">
         <v>125</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F21" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -2074,8 +2231,11 @@
       <c r="E22">
         <v>150</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -2091,8 +2251,11 @@
       <c r="E23">
         <v>175</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -2108,8 +2271,11 @@
       <c r="E24">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F24" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -2125,8 +2291,11 @@
       <c r="E25">
         <v>375</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -2142,8 +2311,11 @@
       <c r="E26">
         <v>400</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -2159,8 +2331,11 @@
       <c r="E27">
         <v>475</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -2176,8 +2351,11 @@
       <c r="E28">
         <v>510</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>75</v>
       </c>
@@ -2185,7 +2363,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -2250,6 +2428,9 @@
         <v>0.1</v>
       </c>
       <c r="C3" s="2"/>
+      <c r="G3" t="s">
+        <v>205</v>
+      </c>
       <c r="H3" s="2">
         <v>0.8</v>
       </c>
@@ -2262,6 +2443,9 @@
         <v>0.2</v>
       </c>
       <c r="C4" s="2"/>
+      <c r="G4" t="s">
+        <v>205</v>
+      </c>
       <c r="H4" s="2">
         <v>0.7</v>
       </c>
@@ -2274,6 +2458,9 @@
         <v>0.3</v>
       </c>
       <c r="C5" s="2"/>
+      <c r="G5" t="s">
+        <v>213</v>
+      </c>
       <c r="H5" s="2">
         <v>0.6</v>
       </c>
@@ -2286,6 +2473,9 @@
         <v>0.4</v>
       </c>
       <c r="C6" s="2"/>
+      <c r="G6" t="s">
+        <v>213</v>
+      </c>
       <c r="H6" s="2">
         <v>0.5</v>
       </c>
@@ -2298,6 +2488,9 @@
         <v>0.5</v>
       </c>
       <c r="C7" s="2"/>
+      <c r="G7" t="s">
+        <v>216</v>
+      </c>
       <c r="H7" s="2">
         <v>0.4</v>
       </c>
@@ -2310,6 +2503,9 @@
         <v>0.6</v>
       </c>
       <c r="C8" s="2"/>
+      <c r="G8" t="s">
+        <v>216</v>
+      </c>
       <c r="H8" s="2">
         <v>0.3</v>
       </c>
@@ -2322,6 +2518,9 @@
         <v>0.7</v>
       </c>
       <c r="C9" s="2"/>
+      <c r="G9" t="s">
+        <v>217</v>
+      </c>
       <c r="H9" s="2">
         <v>0.2</v>
       </c>
@@ -2334,6 +2533,9 @@
         <v>0.8</v>
       </c>
       <c r="C10" s="2"/>
+      <c r="G10" t="s">
+        <v>215</v>
+      </c>
       <c r="H10" s="2">
         <v>0.1</v>
       </c>
@@ -2345,6 +2547,9 @@
       <c r="C11" s="2">
         <v>0.1</v>
       </c>
+      <c r="G11" t="s">
+        <v>205</v>
+      </c>
       <c r="H11" s="2">
         <v>0.8</v>
       </c>
@@ -2356,6 +2561,9 @@
       <c r="C12" s="2">
         <v>0.2</v>
       </c>
+      <c r="G12" t="s">
+        <v>205</v>
+      </c>
       <c r="H12" s="2">
         <v>0.7</v>
       </c>
@@ -2367,6 +2575,9 @@
       <c r="C13" s="2">
         <v>0.3</v>
       </c>
+      <c r="G13" t="s">
+        <v>213</v>
+      </c>
       <c r="H13" s="2">
         <v>0.6</v>
       </c>
@@ -2378,6 +2589,9 @@
       <c r="C14" s="2">
         <v>0.4</v>
       </c>
+      <c r="G14" t="s">
+        <v>213</v>
+      </c>
       <c r="H14" s="2">
         <v>0.5</v>
       </c>
@@ -2389,6 +2603,9 @@
       <c r="C15" s="2">
         <v>0.5</v>
       </c>
+      <c r="G15" t="s">
+        <v>216</v>
+      </c>
       <c r="H15" s="2">
         <v>0.4</v>
       </c>
@@ -2400,6 +2617,9 @@
       <c r="C16" s="2">
         <v>0.6</v>
       </c>
+      <c r="G16" t="s">
+        <v>216</v>
+      </c>
       <c r="H16" s="2">
         <v>0.3</v>
       </c>
@@ -2411,6 +2631,9 @@
       <c r="C17" s="2">
         <v>0.7</v>
       </c>
+      <c r="G17" t="s">
+        <v>217</v>
+      </c>
       <c r="H17" s="2">
         <v>0.2</v>
       </c>
@@ -2422,6 +2645,9 @@
       <c r="C18" s="2">
         <v>0.8</v>
       </c>
+      <c r="G18" t="s">
+        <v>215</v>
+      </c>
       <c r="H18" s="2">
         <v>0.1</v>
       </c>
@@ -2433,6 +2659,9 @@
       <c r="E19" t="s">
         <v>126</v>
       </c>
+      <c r="G19" t="s">
+        <v>205</v>
+      </c>
       <c r="H19" s="2">
         <v>0.8</v>
       </c>
@@ -2444,6 +2673,9 @@
       <c r="E20" t="s">
         <v>127</v>
       </c>
+      <c r="G20" t="s">
+        <v>205</v>
+      </c>
       <c r="H20" s="2">
         <v>0.7</v>
       </c>
@@ -2455,6 +2687,9 @@
       <c r="E21" t="s">
         <v>128</v>
       </c>
+      <c r="G21" t="s">
+        <v>213</v>
+      </c>
       <c r="H21" s="2">
         <v>0.6</v>
       </c>
@@ -2466,6 +2701,9 @@
       <c r="E22" t="s">
         <v>129</v>
       </c>
+      <c r="G22" t="s">
+        <v>213</v>
+      </c>
       <c r="H22" s="2">
         <v>0.5</v>
       </c>
@@ -2477,6 +2715,9 @@
       <c r="E23" t="s">
         <v>130</v>
       </c>
+      <c r="G23" t="s">
+        <v>216</v>
+      </c>
       <c r="H23" s="2">
         <v>0.4</v>
       </c>
@@ -2488,6 +2729,9 @@
       <c r="E24" t="s">
         <v>131</v>
       </c>
+      <c r="G24" t="s">
+        <v>216</v>
+      </c>
       <c r="H24" s="2">
         <v>0.3</v>
       </c>
@@ -2499,6 +2743,9 @@
       <c r="E25" t="s">
         <v>132</v>
       </c>
+      <c r="G25" t="s">
+        <v>217</v>
+      </c>
       <c r="H25" s="2">
         <v>0.2</v>
       </c>
@@ -2510,6 +2757,9 @@
       <c r="E26" t="s">
         <v>133</v>
       </c>
+      <c r="G26" t="s">
+        <v>215</v>
+      </c>
       <c r="H26" s="2">
         <v>0.1</v>
       </c>
@@ -2521,6 +2771,9 @@
       <c r="D27" t="s">
         <v>109</v>
       </c>
+      <c r="G27" t="s">
+        <v>205</v>
+      </c>
       <c r="H27" s="2">
         <v>0.8</v>
       </c>
@@ -2532,6 +2785,9 @@
       <c r="D28" t="s">
         <v>110</v>
       </c>
+      <c r="G28" t="s">
+        <v>205</v>
+      </c>
       <c r="H28" s="2">
         <v>0.7</v>
       </c>
@@ -2543,6 +2799,9 @@
       <c r="D29" t="s">
         <v>111</v>
       </c>
+      <c r="G29" t="s">
+        <v>213</v>
+      </c>
       <c r="H29" s="2">
         <v>0.6</v>
       </c>
@@ -2554,6 +2813,9 @@
       <c r="D30" t="s">
         <v>112</v>
       </c>
+      <c r="G30" t="s">
+        <v>213</v>
+      </c>
       <c r="H30" s="2">
         <v>0.5</v>
       </c>
@@ -2565,6 +2827,9 @@
       <c r="D31" t="s">
         <v>113</v>
       </c>
+      <c r="G31" t="s">
+        <v>216</v>
+      </c>
       <c r="H31" s="2">
         <v>0.4</v>
       </c>
@@ -2576,6 +2841,9 @@
       <c r="D32" t="s">
         <v>114</v>
       </c>
+      <c r="G32" t="s">
+        <v>216</v>
+      </c>
       <c r="H32" s="2">
         <v>0.3</v>
       </c>
@@ -2587,6 +2855,9 @@
       <c r="D33" t="s">
         <v>115</v>
       </c>
+      <c r="G33" t="s">
+        <v>217</v>
+      </c>
       <c r="H33" s="2">
         <v>0.2</v>
       </c>
@@ -2598,6 +2869,9 @@
       <c r="D34" t="s">
         <v>116</v>
       </c>
+      <c r="G34" t="s">
+        <v>215</v>
+      </c>
       <c r="H34" s="2">
         <v>0.1</v>
       </c>
@@ -2609,6 +2883,9 @@
       <c r="D35" t="s">
         <v>117</v>
       </c>
+      <c r="G35" t="s">
+        <v>215</v>
+      </c>
       <c r="H35" s="2">
         <v>0.05</v>
       </c>
@@ -2620,6 +2897,9 @@
       <c r="F36" t="s">
         <v>157</v>
       </c>
+      <c r="G36" t="s">
+        <v>209</v>
+      </c>
       <c r="H36" s="2">
         <v>0.25</v>
       </c>
@@ -2631,6 +2911,9 @@
       <c r="F37" t="s">
         <v>157</v>
       </c>
+      <c r="G37" t="s">
+        <v>209</v>
+      </c>
       <c r="H37" s="2">
         <v>0.25</v>
       </c>
@@ -2642,6 +2925,9 @@
       <c r="F38" t="s">
         <v>157</v>
       </c>
+      <c r="G38" t="s">
+        <v>209</v>
+      </c>
       <c r="H38" s="2">
         <v>0.25</v>
       </c>
@@ -2653,6 +2939,9 @@
       <c r="F39" t="s">
         <v>157</v>
       </c>
+      <c r="G39" t="s">
+        <v>209</v>
+      </c>
       <c r="H39" s="2">
         <v>0.25</v>
       </c>
@@ -2664,6 +2953,9 @@
       <c r="F40" t="s">
         <v>157</v>
       </c>
+      <c r="G40" t="s">
+        <v>209</v>
+      </c>
       <c r="H40" s="2">
         <v>0.25</v>
       </c>
@@ -2675,6 +2967,9 @@
       <c r="F41" t="s">
         <v>157</v>
       </c>
+      <c r="G41" t="s">
+        <v>209</v>
+      </c>
       <c r="H41" s="2">
         <v>0.25</v>
       </c>
@@ -2686,6 +2981,9 @@
       <c r="F42" t="s">
         <v>157</v>
       </c>
+      <c r="G42" t="s">
+        <v>209</v>
+      </c>
       <c r="H42" s="2">
         <v>0.25</v>
       </c>
@@ -2697,6 +2995,9 @@
       <c r="F43" t="s">
         <v>157</v>
       </c>
+      <c r="G43" t="s">
+        <v>209</v>
+      </c>
       <c r="H43" s="2">
         <v>0.25</v>
       </c>
@@ -2708,6 +3009,9 @@
       <c r="F44" t="s">
         <v>157</v>
       </c>
+      <c r="G44" t="s">
+        <v>209</v>
+      </c>
       <c r="H44" s="2">
         <v>0.25</v>
       </c>
@@ -2719,6 +3023,9 @@
       <c r="F45" t="s">
         <v>157</v>
       </c>
+      <c r="G45" t="s">
+        <v>209</v>
+      </c>
       <c r="H45" s="2">
         <v>0.25</v>
       </c>
@@ -2730,6 +3037,9 @@
       <c r="F46" t="s">
         <v>157</v>
       </c>
+      <c r="G46" t="s">
+        <v>209</v>
+      </c>
       <c r="H46" s="2">
         <v>0.25</v>
       </c>
@@ -2741,6 +3051,9 @@
       <c r="F47" t="s">
         <v>157</v>
       </c>
+      <c r="G47" t="s">
+        <v>209</v>
+      </c>
       <c r="H47" s="2">
         <v>0.25</v>
       </c>
@@ -2752,6 +3065,9 @@
       <c r="F48" t="s">
         <v>157</v>
       </c>
+      <c r="G48" t="s">
+        <v>209</v>
+      </c>
       <c r="H48" s="2">
         <v>0.25</v>
       </c>
@@ -2763,6 +3079,9 @@
       <c r="F49" t="s">
         <v>157</v>
       </c>
+      <c r="G49" t="s">
+        <v>209</v>
+      </c>
       <c r="H49" s="2">
         <v>0.25</v>
       </c>
@@ -2773,6 +3092,9 @@
       </c>
       <c r="F50" t="s">
         <v>157</v>
+      </c>
+      <c r="G50" t="s">
+        <v>209</v>
       </c>
       <c r="H50" s="2">
         <v>0.25</v>

--- a/docs/levelups.xlsx
+++ b/docs/levelups.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="weapons" sheetId="1" r:id="rId1"/>
     <sheet name="armor" sheetId="2" r:id="rId2"/>
     <sheet name="other loot" sheetId="3" r:id="rId3"/>
+    <sheet name="spells" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="337">
   <si>
     <t>viking shortsword</t>
   </si>
@@ -676,16 +677,369 @@
   </si>
   <si>
     <t>location</t>
+  </si>
+  <si>
+    <t>rarity</t>
+  </si>
+  <si>
+    <t>Shadow Lash</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Spell</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Fire Bolt</t>
+  </si>
+  <si>
+    <t>Offense</t>
+  </si>
+  <si>
+    <t>Fast single fire projectile</t>
+  </si>
+  <si>
+    <t>Dark Fire</t>
+  </si>
+  <si>
+    <t>Black flames that burn and drain life over time</t>
+  </si>
+  <si>
+    <t>Ash Ward</t>
+  </si>
+  <si>
+    <t>Protection</t>
+  </si>
+  <si>
+    <t>Small barrier that absorbs a few hits</t>
+  </si>
+  <si>
+    <t>Frost Shard</t>
+  </si>
+  <si>
+    <t>Piercing ice projectile that slows</t>
+  </si>
+  <si>
+    <t>Whip of darkness that strikes an arc and knocks back</t>
+  </si>
+  <si>
+    <t>Iron Skin</t>
+  </si>
+  <si>
+    <t>Hardens flesh for a large armor bonus</t>
+  </si>
+  <si>
+    <t>Bone Spear</t>
+  </si>
+  <si>
+    <t>Bone spear that pierces a line of enemies</t>
+  </si>
+  <si>
+    <t>Dispel Hex</t>
+  </si>
+  <si>
+    <t>Cleanses curses, poisons and other debuffs</t>
+  </si>
+  <si>
+    <t>Life Drain</t>
+  </si>
+  <si>
+    <t>Channeled beam that steals health</t>
+  </si>
+  <si>
+    <t>Chain Lightning</t>
+  </si>
+  <si>
+    <t>Lightning that jumps between enemies</t>
+  </si>
+  <si>
+    <t>Bone Armor</t>
+  </si>
+  <si>
+    <t>Orbiting bones that each absorb one hit</t>
+  </si>
+  <si>
+    <t>Plague Cloud</t>
+  </si>
+  <si>
+    <t>Lingering toxic mist that poisons an area</t>
+  </si>
+  <si>
+    <t>Shadow Veil</t>
+  </si>
+  <si>
+    <t>Brief invisibility and high evasion</t>
+  </si>
+  <si>
+    <t>Curse of Frailty</t>
+  </si>
+  <si>
+    <t>Curse</t>
+  </si>
+  <si>
+    <t>Enemies in an area take more damage and hit weaker</t>
+  </si>
+  <si>
+    <t>Fireball</t>
+  </si>
+  <si>
+    <t>Exploding sphere of heavy area fire damage</t>
+  </si>
+  <si>
+    <t>Raise Dead</t>
+  </si>
+  <si>
+    <t>Summon</t>
+  </si>
+  <si>
+    <t>Reanimates fallen enemies as temporary minions</t>
+  </si>
+  <si>
+    <t>Rune of Warding</t>
+  </si>
+  <si>
+    <t>Glyph on the ground that cuts damage taken by allies inside it</t>
+  </si>
+  <si>
+    <t>Blood Nova</t>
+  </si>
+  <si>
+    <t>Spends your health to release a ring of blood magic</t>
+  </si>
+  <si>
+    <t>Mirror of Retribution</t>
+  </si>
+  <si>
+    <t>Reflects projectiles and spells back at attackers</t>
+  </si>
+  <si>
+    <t>Soul Rend</t>
+  </si>
+  <si>
+    <t>Spirit damage that ignores armor</t>
+  </si>
+  <si>
+    <t>Blizzard</t>
+  </si>
+  <si>
+    <t>Sustained ice storm over a wide area</t>
+  </si>
+  <si>
+    <t>Corpse Explosion</t>
+  </si>
+  <si>
+    <t>Detonates corpses for massive area damage</t>
+  </si>
+  <si>
+    <t>Spectral Bulwark</t>
+  </si>
+  <si>
+    <t>Huge shield that absorbs damage for the whole party</t>
+  </si>
+  <si>
+    <t>Hellfire Pillar</t>
+  </si>
+  <si>
+    <t>Column of infernal flame that leaves burning ground</t>
+  </si>
+  <si>
+    <t>Void Rift</t>
+  </si>
+  <si>
+    <t>Tear in reality that pulls enemies in and crushes them</t>
+  </si>
+  <si>
+    <t>Undying Pact</t>
+  </si>
+  <si>
+    <t>Cheats death once, reviving you at partial health</t>
+  </si>
+  <si>
+    <t>Summon Abyssal Knight</t>
+  </si>
+  <si>
+    <t>Permanent demonic or undead champion</t>
+  </si>
+  <si>
+    <t>Meteor Storm</t>
+  </si>
+  <si>
+    <t>Burning meteors rain across the battlefield</t>
+  </si>
+  <si>
+    <t>Null Sanctum</t>
+  </si>
+  <si>
+    <t>Zone where allies are briefly immune to all damage</t>
+  </si>
+  <si>
+    <t>Apocalypse / Eclipse of Ruin</t>
+  </si>
+  <si>
+    <t>Ultimate that devastates every enemy on screen</t>
+  </si>
+  <si>
+    <t>Drop Chance</t>
+  </si>
+  <si>
+    <t>magic potency ring 1</t>
+  </si>
+  <si>
+    <t>magic potency ring 2</t>
+  </si>
+  <si>
+    <t>magic potency ring 3</t>
+  </si>
+  <si>
+    <t>magic potency ring 4</t>
+  </si>
+  <si>
+    <t>magic potency ring 5</t>
+  </si>
+  <si>
+    <t>magic potency ring 6</t>
+  </si>
+  <si>
+    <t>magic potency ring 7</t>
+  </si>
+  <si>
+    <t>magic potency ring 8</t>
+  </si>
+  <si>
+    <t>magic potency ring 9</t>
+  </si>
+  <si>
+    <t>magic potency ring 10</t>
+  </si>
+  <si>
+    <t>hp potency ring 1</t>
+  </si>
+  <si>
+    <t>hp potency ring 2</t>
+  </si>
+  <si>
+    <t>hp potency ring 3</t>
+  </si>
+  <si>
+    <t>hp potency ring 4</t>
+  </si>
+  <si>
+    <t>hp potency ring 5</t>
+  </si>
+  <si>
+    <t>hp potency ring 6</t>
+  </si>
+  <si>
+    <t>hp potency ring 7</t>
+  </si>
+  <si>
+    <t>hp potency ring 8</t>
+  </si>
+  <si>
+    <t>hp potency ring 9</t>
+  </si>
+  <si>
+    <t>hp potency ring 10</t>
+  </si>
+  <si>
+    <t>tier 1</t>
+  </si>
+  <si>
+    <t>tier 2</t>
+  </si>
+  <si>
+    <t>tier 3</t>
+  </si>
+  <si>
+    <t>tier 4</t>
+  </si>
+  <si>
+    <t>tier 5</t>
+  </si>
+  <si>
+    <t>mana effect</t>
+  </si>
+  <si>
+    <t>hp effect</t>
+  </si>
+  <si>
+    <t>character</t>
+  </si>
+  <si>
+    <t>all spellcasters</t>
+  </si>
+  <si>
+    <t>warrior, warlock</t>
+  </si>
+  <si>
+    <t>dexterity ring 1</t>
+  </si>
+  <si>
+    <t>dexterity ring 2</t>
+  </si>
+  <si>
+    <t>dexterity ring 3</t>
+  </si>
+  <si>
+    <t>dexterity ring 4</t>
+  </si>
+  <si>
+    <t>dexterity ring 5</t>
+  </si>
+  <si>
+    <t>dexterity ring 6</t>
+  </si>
+  <si>
+    <t>dexterity ring 7</t>
+  </si>
+  <si>
+    <t>dexterity ring 8</t>
+  </si>
+  <si>
+    <t>dexterity ring 9</t>
+  </si>
+  <si>
+    <t>dexterity ring 10</t>
+  </si>
+  <si>
+    <t>ranged weapon damage</t>
+  </si>
+  <si>
+    <t>rogue</t>
+  </si>
+  <si>
+    <t>Mana Cost</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Instant</t>
+  </si>
+  <si>
+    <t>Permanent</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="00000"/>
+    <numFmt numFmtId="169" formatCode="0&quot; s&quot;;;&quot;None&quot;"/>
+    <numFmt numFmtId="170" formatCode="0&quot; s&quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -701,16 +1055,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F2F3A"/>
+        <bgColor rgb="FF333300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -718,11 +1102,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -731,6 +1130,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1291,7 +1720,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G11">
         <v>97</v>
@@ -2381,14 +2810,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.59765625" customWidth="1"/>
     <col min="2" max="2" width="18.06640625" customWidth="1"/>
     <col min="3" max="3" width="14.86328125" customWidth="1"/>
     <col min="4" max="4" width="17.46484375" customWidth="1"/>
-    <col min="5" max="5" width="14.53125" customWidth="1"/>
+    <col min="5" max="5" width="17.59765625" customWidth="1"/>
     <col min="6" max="6" width="28.53125" customWidth="1"/>
     <col min="7" max="7" width="15.06640625" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" customWidth="1"/>
@@ -3345,62 +3774,1421 @@
         <v>193</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A111" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>290</v>
+      </c>
+      <c r="C112" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E112" t="s">
+        <v>318</v>
+      </c>
+      <c r="G112" t="s">
+        <v>310</v>
+      </c>
+      <c r="H112" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>291</v>
+      </c>
+      <c r="C113" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E113" t="s">
+        <v>318</v>
+      </c>
+      <c r="G113" t="s">
+        <v>310</v>
+      </c>
+      <c r="H113" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>292</v>
+      </c>
+      <c r="C114" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E114" t="s">
+        <v>318</v>
+      </c>
+      <c r="G114" t="s">
+        <v>311</v>
+      </c>
+      <c r="H114" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>293</v>
+      </c>
+      <c r="C115" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E115" t="s">
+        <v>318</v>
+      </c>
+      <c r="G115" t="s">
+        <v>311</v>
+      </c>
+      <c r="H115" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>294</v>
+      </c>
+      <c r="C116" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E116" t="s">
+        <v>318</v>
+      </c>
+      <c r="G116" t="s">
+        <v>312</v>
+      </c>
+      <c r="H116" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>295</v>
+      </c>
+      <c r="C117" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E117" t="s">
+        <v>318</v>
+      </c>
+      <c r="G117" t="s">
+        <v>312</v>
+      </c>
+      <c r="H117" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>296</v>
+      </c>
+      <c r="C118" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="E118" t="s">
+        <v>318</v>
+      </c>
+      <c r="G118" t="s">
+        <v>313</v>
+      </c>
+      <c r="H118" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>297</v>
+      </c>
+      <c r="C119" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E119" t="s">
+        <v>318</v>
+      </c>
+      <c r="G119" t="s">
+        <v>313</v>
+      </c>
+      <c r="H119" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>298</v>
+      </c>
+      <c r="C120" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E120" t="s">
+        <v>318</v>
+      </c>
+      <c r="G120" t="s">
+        <v>314</v>
+      </c>
+      <c r="H120" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>299</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="E121" t="s">
+        <v>318</v>
+      </c>
+      <c r="G121" t="s">
+        <v>314</v>
+      </c>
+      <c r="H121" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>300</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E123" t="s">
+        <v>319</v>
+      </c>
+      <c r="G123" t="s">
+        <v>310</v>
+      </c>
+      <c r="H123" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>301</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E124" t="s">
+        <v>319</v>
+      </c>
+      <c r="G124" t="s">
+        <v>310</v>
+      </c>
+      <c r="H124" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>302</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E125" t="s">
+        <v>319</v>
+      </c>
+      <c r="G125" t="s">
+        <v>311</v>
+      </c>
+      <c r="H125" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>303</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E126" t="s">
+        <v>319</v>
+      </c>
+      <c r="G126" t="s">
+        <v>311</v>
+      </c>
+      <c r="H126" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>304</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E127" t="s">
+        <v>319</v>
+      </c>
+      <c r="G127" t="s">
+        <v>312</v>
+      </c>
+      <c r="H127" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>305</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E128" t="s">
+        <v>319</v>
+      </c>
+      <c r="G128" t="s">
+        <v>312</v>
+      </c>
+      <c r="H128" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>306</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="E129" t="s">
+        <v>319</v>
+      </c>
+      <c r="G129" t="s">
+        <v>313</v>
+      </c>
+      <c r="H129" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>307</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E130" t="s">
+        <v>319</v>
+      </c>
+      <c r="G130" t="s">
+        <v>313</v>
+      </c>
+      <c r="H130" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>308</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E131" t="s">
+        <v>319</v>
+      </c>
+      <c r="G131" t="s">
+        <v>314</v>
+      </c>
+      <c r="H131" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>309</v>
+      </c>
+      <c r="D132" s="2">
+        <v>1</v>
+      </c>
+      <c r="E132" t="s">
+        <v>319</v>
+      </c>
+      <c r="G132" t="s">
+        <v>314</v>
+      </c>
+      <c r="H132" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>320</v>
+      </c>
+      <c r="B135" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E135" t="s">
+        <v>331</v>
+      </c>
+      <c r="G135" t="s">
+        <v>310</v>
+      </c>
+      <c r="H135" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>321</v>
+      </c>
+      <c r="B136" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E136" t="s">
+        <v>331</v>
+      </c>
+      <c r="G136" t="s">
+        <v>310</v>
+      </c>
+      <c r="H136" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>322</v>
+      </c>
+      <c r="B137" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E137" t="s">
+        <v>331</v>
+      </c>
+      <c r="G137" t="s">
+        <v>311</v>
+      </c>
+      <c r="H137" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>323</v>
+      </c>
+      <c r="B138" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E138" t="s">
+        <v>331</v>
+      </c>
+      <c r="G138" t="s">
+        <v>311</v>
+      </c>
+      <c r="H138" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>324</v>
+      </c>
+      <c r="B139" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E139" t="s">
+        <v>331</v>
+      </c>
+      <c r="G139" t="s">
+        <v>312</v>
+      </c>
+      <c r="H139" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>325</v>
+      </c>
+      <c r="B140" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E140" t="s">
+        <v>331</v>
+      </c>
+      <c r="G140" t="s">
+        <v>312</v>
+      </c>
+      <c r="H140" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>326</v>
+      </c>
+      <c r="B141" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="E141" t="s">
+        <v>331</v>
+      </c>
+      <c r="G141" t="s">
+        <v>313</v>
+      </c>
+      <c r="H141" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>327</v>
+      </c>
+      <c r="B142" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E142" t="s">
+        <v>331</v>
+      </c>
+      <c r="G142" t="s">
+        <v>313</v>
+      </c>
+      <c r="H142" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>328</v>
+      </c>
+      <c r="B143" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E143" t="s">
+        <v>331</v>
+      </c>
+      <c r="G143" t="s">
+        <v>314</v>
+      </c>
+      <c r="H143" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>329</v>
+      </c>
+      <c r="B144" s="2">
+        <v>1</v>
+      </c>
+      <c r="E144" t="s">
+        <v>331</v>
+      </c>
+      <c r="G144" t="s">
+        <v>314</v>
+      </c>
+      <c r="H144" s="2">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="18.46484375" customWidth="1"/>
+    <col min="2" max="2" width="32.59765625" customWidth="1"/>
+    <col min="3" max="3" width="14.9296875" customWidth="1"/>
+    <col min="4" max="4" width="18.1328125" customWidth="1"/>
+    <col min="5" max="5" width="18.19921875" customWidth="1"/>
+    <col min="6" max="6" width="12.86328125" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="12">
+        <v>0.125</v>
+      </c>
+      <c r="F2" s="13">
+        <v>7</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0.115</v>
+      </c>
+      <c r="F3" s="13">
+        <v>12</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.11</v>
+      </c>
+      <c r="F4" s="13">
+        <v>15</v>
+      </c>
+      <c r="G4" s="14">
+        <v>10</v>
+      </c>
+      <c r="H4" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="13">
+        <v>14</v>
+      </c>
+      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="13">
+        <v>18</v>
+      </c>
+      <c r="G6" s="14">
+        <v>2</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="12">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="F7" s="13">
+        <v>22</v>
+      </c>
+      <c r="G7" s="14">
+        <v>15</v>
+      </c>
+      <c r="H7" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="12">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="F8" s="13">
+        <v>20</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="F9" s="13">
+        <v>25</v>
+      </c>
+      <c r="G9" s="14">
+        <v>12</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="F10" s="13">
+        <v>24</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3</v>
+      </c>
+      <c r="H10" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="F11" s="13">
+        <v>30</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E12" s="12">
+        <v>2.75E-2</v>
+      </c>
+      <c r="F12" s="13">
+        <v>35</v>
+      </c>
+      <c r="G12" s="14">
+        <v>20</v>
+      </c>
+      <c r="H12" s="16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E13" s="12">
+        <v>2.75E-2</v>
+      </c>
+      <c r="F13" s="13">
+        <v>38</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E14" s="12">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F14" s="13">
+        <v>40</v>
+      </c>
+      <c r="G14" s="14">
+        <v>25</v>
+      </c>
+      <c r="H14" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E15" s="12">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F15" s="13">
+        <v>42</v>
+      </c>
+      <c r="G15" s="14">
+        <v>10</v>
+      </c>
+      <c r="H15" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="E16" s="12">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F16" s="13">
+        <v>45</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E17" s="12">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F17" s="13">
+        <v>55</v>
+      </c>
+      <c r="G17" s="14">
+        <v>20</v>
+      </c>
+      <c r="H17" s="16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="54.75" x14ac:dyDescent="0.45">
+      <c r="A18" s="8">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" s="12">
+        <v>1.4E-2</v>
+      </c>
+      <c r="F18" s="13">
+        <v>60</v>
+      </c>
+      <c r="G18" s="14">
+        <v>30</v>
+      </c>
+      <c r="H18" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F19" s="13">
+        <v>28</v>
+      </c>
+      <c r="G19" s="14">
+        <v>8</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A20" s="8">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F20" s="13">
+        <v>70</v>
+      </c>
+      <c r="G20" s="14">
+        <v>35</v>
+      </c>
+      <c r="H20" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E21" s="12">
+        <v>1.2E-2</v>
+      </c>
+      <c r="F21" s="13">
+        <v>65</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" s="12">
+        <v>1.2E-2</v>
+      </c>
+      <c r="F22" s="13">
+        <v>80</v>
+      </c>
+      <c r="G22" s="14">
+        <v>12</v>
+      </c>
+      <c r="H22" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E23" s="12">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F23" s="13">
+        <v>75</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A24" s="8">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E24" s="12">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="F24" s="13">
+        <v>100</v>
+      </c>
+      <c r="G24" s="14">
+        <v>60</v>
+      </c>
+      <c r="H24" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" s="12">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="F25" s="13">
+        <v>110</v>
+      </c>
+      <c r="G25" s="14">
+        <v>15</v>
+      </c>
+      <c r="H25" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E26" s="12">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F26" s="13">
+        <v>120</v>
+      </c>
+      <c r="G26" s="14">
+        <v>20</v>
+      </c>
+      <c r="H26" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A27" s="8">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F27" s="13">
+        <v>150</v>
+      </c>
+      <c r="G27" s="14">
+        <v>180</v>
+      </c>
+      <c r="H27" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E28" s="12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F28" s="13">
+        <v>160</v>
+      </c>
+      <c r="G28" s="14">
+        <v>90</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="E29" s="12">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F29" s="13">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>45</v>
+      </c>
+      <c r="H29" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A30" s="8">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="E30" s="12">
+        <v>1.5E-3</v>
+      </c>
+      <c r="F30" s="13">
+        <v>220</v>
+      </c>
+      <c r="G30" s="14">
+        <v>120</v>
+      </c>
+      <c r="H30" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="41.25" x14ac:dyDescent="0.45">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E31" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F31" s="13">
+        <v>300</v>
+      </c>
+      <c r="G31" s="14">
+        <v>300</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/levelups.xlsx
+++ b/docs/levelups.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="weapons" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="356">
   <si>
     <t>viking shortsword</t>
   </si>
@@ -1028,6 +1028,63 @@
   </si>
   <si>
     <t>Permanent</t>
+  </si>
+  <si>
+    <t>shield name</t>
+  </si>
+  <si>
+    <t>Broddi's Shield</t>
+  </si>
+  <si>
+    <t>Scutum</t>
+  </si>
+  <si>
+    <t>Crusader Shield</t>
+  </si>
+  <si>
+    <t>War Tower Shield</t>
+  </si>
+  <si>
+    <t>Plate Knight's Shield</t>
+  </si>
+  <si>
+    <t>Lady Knight's Shield</t>
+  </si>
+  <si>
+    <t>Kite Shield</t>
+  </si>
+  <si>
+    <t>Desert Shield</t>
+  </si>
+  <si>
+    <t>Heater Shield</t>
+  </si>
+  <si>
+    <t>Eastern Shield</t>
+  </si>
+  <si>
+    <t>Beast Shield</t>
+  </si>
+  <si>
+    <t>Rider's Shield</t>
+  </si>
+  <si>
+    <t>War Camp Shield</t>
+  </si>
+  <si>
+    <t>Heraldic Shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dock Shield</t>
+  </si>
+  <si>
+    <t>Viking Shield (iron-bound)</t>
+  </si>
+  <si>
+    <t>Village Shields (blue-white, red, green</t>
+  </si>
+  <si>
+    <t>Viking Round, Painted Viking, Viking (green and white)</t>
   </si>
 </sst>
 </file>
@@ -1036,8 +1093,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="00000"/>
-    <numFmt numFmtId="169" formatCode="0&quot; s&quot;;;&quot;None&quot;"/>
-    <numFmt numFmtId="170" formatCode="0&quot; s&quot;"/>
+    <numFmt numFmtId="165" formatCode="0&quot; s&quot;;;&quot;None&quot;"/>
+    <numFmt numFmtId="166" formatCode="0&quot; s&quot;"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1152,13 +1209,13 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2213,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.06640625" customWidth="1"/>
@@ -2797,9 +2854,275 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="57" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>338</v>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>339</v>
+      </c>
+      <c r="C39">
+        <v>9</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>340</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>341</v>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>342</v>
+      </c>
+      <c r="C42">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>343</v>
+      </c>
+      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>344</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>345</v>
+      </c>
+      <c r="C45">
+        <v>6</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>346</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>347</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>7</v>
+      </c>
+      <c r="E47">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>348</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>8</v>
+      </c>
+      <c r="E48">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>349</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+      <c r="E50">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>351</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>7</v>
+      </c>
+      <c r="E52">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A54" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>7</v>
+      </c>
+      <c r="E54">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A55" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55">
+        <v>7</v>
+      </c>
+      <c r="E55">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
